--- a/T41_V012_Files/T41_V012_BOMs/Source Files/T41_RF_Board_BOM_V012.6_03-07-25.xlsx
+++ b/T41_V012_Files/T41_V012_BOMs/Source Files/T41_RF_Board_BOM_V012.6_03-07-25.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dad\Documents\GitHub\T41\T41_V012_Files\T41_V012_BOMs\Source Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EFCC7F8-74C8-4046-B8F8-82F400E8F9C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B038313-A941-4B23-9A05-F5903F8B04ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="347">
   <si>
     <t>T41 V012.6 RF Board Parts (Less PCB)</t>
   </si>
@@ -565,9 +565,6 @@
   </si>
   <si>
     <t>Thick Film Resistors - SMD 1/4Watt 100Kohms 1% Commercial Use</t>
-  </si>
-  <si>
-    <t>1.8K Ohm SMD 1206 Resistor</t>
   </si>
   <si>
     <t>R56</t>
@@ -1096,6 +1093,12 @@
   </si>
   <si>
     <t>584-AD8599ARZ-R</t>
+  </si>
+  <si>
+    <t>2.7K Ohm SMD 1206 Resistor</t>
+  </si>
+  <si>
+    <t>652-CR1206FX-2701ELF</t>
   </si>
 </sst>
 </file>
@@ -1744,7 +1747,7 @@
         <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D12" s="4">
         <f>'Board As Second RX'!A39</f>
@@ -1858,10 +1861,10 @@
         <v>0</v>
       </c>
       <c r="B3" s="24" t="s">
+        <v>333</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>334</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>335</v>
       </c>
       <c r="D3" t="s">
         <v>166</v>
@@ -1915,7 +1918,7 @@
         <v>33</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D5" t="s">
         <v>35</v>
@@ -1945,13 +1948,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
+        <v>331</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>333</v>
-      </c>
       <c r="D6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G6" s="11"/>
       <c r="H6" s="11"/>
@@ -1961,13 +1964,13 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G7" s="11">
         <v>0.17</v>
@@ -1994,13 +1997,13 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
+        <v>324</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="D8" t="s">
         <v>325</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="D8" t="s">
-        <v>326</v>
       </c>
       <c r="G8" s="11">
         <v>0.17</v>
@@ -2018,7 +2021,7 @@
         <v>41</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D9" t="s">
         <v>42</v>
@@ -2237,10 +2240,10 @@
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F16" t="s">
         <v>87</v>
@@ -2366,16 +2369,16 @@
         <v>3</v>
       </c>
       <c r="B21" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>102</v>
       </c>
       <c r="D21" t="s">
+        <v>329</v>
+      </c>
+      <c r="E21" t="s">
         <v>330</v>
-      </c>
-      <c r="E21" t="s">
-        <v>331</v>
       </c>
       <c r="G21" s="11">
         <v>0.47</v>
@@ -2768,7 +2771,7 @@
         <v>164</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D33" t="s">
         <v>166</v>
@@ -2801,7 +2804,7 @@
         <v>169</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D34" t="s">
         <v>170</v>
@@ -2831,13 +2834,13 @@
         <v>1</v>
       </c>
       <c r="B35" t="s">
+        <v>345</v>
+      </c>
+      <c r="C35" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="C35" s="8" t="s">
-        <v>174</v>
-      </c>
       <c r="D35" t="s">
-        <v>175</v>
+        <v>346</v>
       </c>
       <c r="G35" s="11">
         <v>0.1</v>
@@ -2847,16 +2850,16 @@
         <v>0.1</v>
       </c>
       <c r="I35" t="s">
+        <v>174</v>
+      </c>
+      <c r="J35" t="s">
         <v>175</v>
-      </c>
-      <c r="J35" t="s">
-        <v>176</v>
       </c>
       <c r="K35" t="s">
         <v>121</v>
       </c>
       <c r="L35" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.35">
@@ -2864,13 +2867,13 @@
         <v>1</v>
       </c>
       <c r="B36" t="s">
+        <v>177</v>
+      </c>
+      <c r="C36" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="D36" t="s">
         <v>179</v>
-      </c>
-      <c r="D36" t="s">
-        <v>180</v>
       </c>
       <c r="G36" s="11">
         <v>0.1</v>
@@ -2880,16 +2883,16 @@
         <v>0.1</v>
       </c>
       <c r="I36" t="s">
+        <v>179</v>
+      </c>
+      <c r="J36" t="s">
         <v>180</v>
-      </c>
-      <c r="J36" t="s">
-        <v>181</v>
       </c>
       <c r="K36" t="s">
         <v>121</v>
       </c>
       <c r="L36" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.35">
@@ -2897,13 +2900,13 @@
         <v>1</v>
       </c>
       <c r="B37" t="s">
+        <v>182</v>
+      </c>
+      <c r="C37" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="D37" t="s">
         <v>184</v>
-      </c>
-      <c r="D37" t="s">
-        <v>185</v>
       </c>
       <c r="G37" s="11">
         <v>0.1</v>
@@ -2913,16 +2916,16 @@
         <v>0.1</v>
       </c>
       <c r="I37" t="s">
+        <v>184</v>
+      </c>
+      <c r="J37" t="s">
         <v>185</v>
-      </c>
-      <c r="J37" t="s">
-        <v>186</v>
       </c>
       <c r="K37" t="s">
         <v>121</v>
       </c>
       <c r="L37" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.35">
@@ -2930,13 +2933,13 @@
         <v>1</v>
       </c>
       <c r="B38" t="s">
+        <v>187</v>
+      </c>
+      <c r="C38" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="D38" t="s">
         <v>189</v>
-      </c>
-      <c r="D38" t="s">
-        <v>190</v>
       </c>
       <c r="G38" s="11">
         <v>0.1</v>
@@ -2946,16 +2949,16 @@
         <v>0.1</v>
       </c>
       <c r="I38" t="s">
+        <v>189</v>
+      </c>
+      <c r="J38" t="s">
         <v>190</v>
-      </c>
-      <c r="J38" t="s">
-        <v>191</v>
       </c>
       <c r="K38" t="s">
         <v>121</v>
       </c>
       <c r="L38" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="29" x14ac:dyDescent="0.35">
@@ -2963,13 +2966,13 @@
         <v>18</v>
       </c>
       <c r="B39" t="s">
+        <v>192</v>
+      </c>
+      <c r="C39" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="F39" t="s">
         <v>194</v>
-      </c>
-      <c r="F39" t="s">
-        <v>195</v>
       </c>
       <c r="G39" s="11">
         <v>2.8000000000000001E-2</v>
@@ -2984,13 +2987,13 @@
         <v>1</v>
       </c>
       <c r="B40" t="s">
+        <v>195</v>
+      </c>
+      <c r="C40" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="C40" s="8" t="s">
+      <c r="D40" t="s">
         <v>197</v>
-      </c>
-      <c r="D40" t="s">
-        <v>198</v>
       </c>
       <c r="G40" s="11">
         <v>4.0199999999999996</v>
@@ -3000,16 +3003,16 @@
         <v>4.0199999999999996</v>
       </c>
       <c r="I40" t="s">
+        <v>197</v>
+      </c>
+      <c r="J40" t="s">
+        <v>195</v>
+      </c>
+      <c r="K40" t="s">
         <v>198</v>
       </c>
-      <c r="J40" t="s">
-        <v>196</v>
-      </c>
-      <c r="K40" t="s">
+      <c r="L40" t="s">
         <v>199</v>
-      </c>
-      <c r="L40" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.35">
@@ -3017,13 +3020,13 @@
         <v>1</v>
       </c>
       <c r="B41" t="s">
+        <v>200</v>
+      </c>
+      <c r="C41" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="C41" s="8" t="s">
+      <c r="D41" t="s">
         <v>202</v>
-      </c>
-      <c r="D41" t="s">
-        <v>203</v>
       </c>
       <c r="G41" s="11">
         <v>5.17</v>
@@ -3033,16 +3036,16 @@
         <v>5.17</v>
       </c>
       <c r="I41" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J41" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K41" t="s">
+        <v>198</v>
+      </c>
+      <c r="L41" t="s">
         <v>199</v>
-      </c>
-      <c r="L41" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.35">
@@ -3050,16 +3053,16 @@
         <v>2</v>
       </c>
       <c r="B42" t="s">
+        <v>203</v>
+      </c>
+      <c r="C42" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="D42" t="s">
         <v>205</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
         <v>206</v>
-      </c>
-      <c r="E42" t="s">
-        <v>207</v>
       </c>
       <c r="G42" s="11">
         <v>0.85</v>
@@ -3074,13 +3077,13 @@
         <v>1</v>
       </c>
       <c r="B43" t="s">
+        <v>207</v>
+      </c>
+      <c r="C43" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="C43" s="8" t="s">
+      <c r="D43" t="s">
         <v>209</v>
-      </c>
-      <c r="D43" t="s">
-        <v>210</v>
       </c>
       <c r="G43" s="11">
         <v>3.6</v>
@@ -3090,16 +3093,16 @@
         <v>3.6</v>
       </c>
       <c r="I43" t="s">
+        <v>209</v>
+      </c>
+      <c r="J43" t="s">
+        <v>207</v>
+      </c>
+      <c r="K43" t="s">
+        <v>198</v>
+      </c>
+      <c r="L43" t="s">
         <v>210</v>
-      </c>
-      <c r="J43" t="s">
-        <v>208</v>
-      </c>
-      <c r="K43" t="s">
-        <v>199</v>
-      </c>
-      <c r="L43" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.35">
@@ -3107,13 +3110,13 @@
         <v>2</v>
       </c>
       <c r="B44" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C44" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="D44" t="s">
         <v>212</v>
-      </c>
-      <c r="D44" t="s">
-        <v>213</v>
       </c>
       <c r="E44" t="s">
         <v>71</v>
@@ -3126,16 +3129,16 @@
         <v>10.64</v>
       </c>
       <c r="I44" t="s">
+        <v>212</v>
+      </c>
+      <c r="J44" t="s">
         <v>213</v>
       </c>
-      <c r="J44" t="s">
+      <c r="K44" t="s">
         <v>214</v>
       </c>
-      <c r="K44" t="s">
+      <c r="L44" t="s">
         <v>215</v>
-      </c>
-      <c r="L44" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.35">
@@ -3143,13 +3146,13 @@
         <v>2</v>
       </c>
       <c r="B45" t="s">
+        <v>216</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="D45" s="13" t="s">
         <v>217</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="D45" s="13" t="s">
-        <v>218</v>
       </c>
       <c r="E45" t="s">
         <v>71</v>
@@ -3162,16 +3165,16 @@
         <v>0.66</v>
       </c>
       <c r="I45" t="s">
+        <v>218</v>
+      </c>
+      <c r="J45" t="s">
         <v>219</v>
       </c>
-      <c r="J45" t="s">
+      <c r="K45" t="s">
         <v>220</v>
       </c>
-      <c r="K45" t="s">
+      <c r="L45" t="s">
         <v>221</v>
-      </c>
-      <c r="L45" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.35">
@@ -3179,13 +3182,13 @@
         <v>2</v>
       </c>
       <c r="B46" t="s">
+        <v>222</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="D46" t="s">
         <v>223</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>341</v>
-      </c>
-      <c r="D46" t="s">
-        <v>224</v>
       </c>
       <c r="G46" s="11">
         <v>0.84</v>
@@ -3195,16 +3198,16 @@
         <v>1.68</v>
       </c>
       <c r="I46" t="s">
+        <v>224</v>
+      </c>
+      <c r="J46" t="s">
         <v>225</v>
       </c>
-      <c r="J46" t="s">
+      <c r="K46" t="s">
+        <v>220</v>
+      </c>
+      <c r="L46" t="s">
         <v>226</v>
-      </c>
-      <c r="K46" t="s">
-        <v>221</v>
-      </c>
-      <c r="L46" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.35">
@@ -3212,13 +3215,13 @@
         <v>1</v>
       </c>
       <c r="B47" t="s">
+        <v>227</v>
+      </c>
+      <c r="C47" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="C47" s="8" t="s">
+      <c r="D47" t="s">
         <v>229</v>
-      </c>
-      <c r="D47" t="s">
-        <v>230</v>
       </c>
       <c r="G47" s="11">
         <v>0.47</v>
@@ -3233,13 +3236,13 @@
         <v>2</v>
       </c>
       <c r="B48" t="s">
+        <v>230</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="D48" t="s">
         <v>231</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="D48" t="s">
-        <v>232</v>
       </c>
       <c r="G48" s="11">
         <v>1.03</v>
@@ -3249,16 +3252,16 @@
         <v>2.06</v>
       </c>
       <c r="I48" t="s">
+        <v>231</v>
+      </c>
+      <c r="J48" t="s">
         <v>232</v>
       </c>
-      <c r="J48" t="s">
+      <c r="K48" t="s">
         <v>233</v>
       </c>
-      <c r="K48" t="s">
+      <c r="L48" t="s">
         <v>234</v>
-      </c>
-      <c r="L48" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.35">
@@ -3266,13 +3269,13 @@
         <v>1</v>
       </c>
       <c r="B49" t="s">
+        <v>235</v>
+      </c>
+      <c r="C49" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="C49" s="8" t="s">
+      <c r="D49" t="s">
         <v>237</v>
-      </c>
-      <c r="D49" t="s">
-        <v>238</v>
       </c>
       <c r="G49" s="11">
         <v>2.14</v>
@@ -3282,16 +3285,16 @@
         <v>2.14</v>
       </c>
       <c r="I49" t="s">
+        <v>237</v>
+      </c>
+      <c r="J49" t="s">
         <v>238</v>
       </c>
-      <c r="J49" t="s">
+      <c r="K49" t="s">
         <v>239</v>
       </c>
-      <c r="K49" t="s">
+      <c r="L49" t="s">
         <v>240</v>
-      </c>
-      <c r="L49" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.35">
@@ -3299,13 +3302,13 @@
         <v>1</v>
       </c>
       <c r="B50" t="s">
+        <v>241</v>
+      </c>
+      <c r="C50" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="C50" s="8" t="s">
+      <c r="D50" t="s">
         <v>243</v>
-      </c>
-      <c r="D50" t="s">
-        <v>244</v>
       </c>
       <c r="G50" s="11">
         <v>1.87</v>
@@ -3315,16 +3318,16 @@
         <v>1.87</v>
       </c>
       <c r="I50" t="s">
+        <v>243</v>
+      </c>
+      <c r="J50" t="s">
+        <v>241</v>
+      </c>
+      <c r="K50" t="s">
+        <v>198</v>
+      </c>
+      <c r="L50" t="s">
         <v>244</v>
-      </c>
-      <c r="J50" t="s">
-        <v>242</v>
-      </c>
-      <c r="K50" t="s">
-        <v>199</v>
-      </c>
-      <c r="L50" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.35">
@@ -3332,13 +3335,13 @@
         <v>1</v>
       </c>
       <c r="B51" t="s">
+        <v>245</v>
+      </c>
+      <c r="C51" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="C51" s="8" t="s">
+      <c r="D51" t="s">
         <v>247</v>
-      </c>
-      <c r="D51" t="s">
-        <v>248</v>
       </c>
       <c r="G51" s="11">
         <v>2.46</v>
@@ -3348,16 +3351,16 @@
         <v>2.46</v>
       </c>
       <c r="I51" t="s">
+        <v>247</v>
+      </c>
+      <c r="J51" t="s">
+        <v>245</v>
+      </c>
+      <c r="K51" t="s">
+        <v>220</v>
+      </c>
+      <c r="L51" t="s">
         <v>248</v>
-      </c>
-      <c r="J51" t="s">
-        <v>246</v>
-      </c>
-      <c r="K51" t="s">
-        <v>221</v>
-      </c>
-      <c r="L51" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.35">
@@ -3365,13 +3368,13 @@
         <v>1</v>
       </c>
       <c r="B52" t="s">
+        <v>249</v>
+      </c>
+      <c r="C52" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="C52" s="8" t="s">
+      <c r="D52" t="s">
         <v>251</v>
-      </c>
-      <c r="D52" t="s">
-        <v>252</v>
       </c>
       <c r="G52" s="11">
         <v>1.69</v>
@@ -3381,16 +3384,16 @@
         <v>1.69</v>
       </c>
       <c r="I52" t="s">
+        <v>251</v>
+      </c>
+      <c r="J52" t="s">
         <v>252</v>
       </c>
-      <c r="J52" t="s">
+      <c r="K52" t="s">
+        <v>220</v>
+      </c>
+      <c r="L52" t="s">
         <v>253</v>
-      </c>
-      <c r="K52" t="s">
-        <v>221</v>
-      </c>
-      <c r="L52" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.35">
@@ -3398,13 +3401,13 @@
         <v>1</v>
       </c>
       <c r="B53" t="s">
+        <v>254</v>
+      </c>
+      <c r="C53" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="C53" s="8" t="s">
+      <c r="D53" t="s">
         <v>256</v>
-      </c>
-      <c r="D53" t="s">
-        <v>257</v>
       </c>
       <c r="G53" s="11">
         <v>0.46</v>
@@ -3414,16 +3417,16 @@
         <v>0.46</v>
       </c>
       <c r="I53" t="s">
+        <v>257</v>
+      </c>
+      <c r="J53" t="s">
         <v>258</v>
-      </c>
-      <c r="J53" t="s">
-        <v>259</v>
       </c>
       <c r="K53" t="s">
         <v>110</v>
       </c>
       <c r="L53" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.35">
@@ -3431,13 +3434,13 @@
         <v>1</v>
       </c>
       <c r="B54" t="s">
+        <v>260</v>
+      </c>
+      <c r="C54" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="C54" s="8" t="s">
+      <c r="D54" t="s">
         <v>262</v>
-      </c>
-      <c r="D54" t="s">
-        <v>263</v>
       </c>
       <c r="G54" s="11">
         <v>1.42</v>
@@ -3447,16 +3450,16 @@
         <v>1.42</v>
       </c>
       <c r="I54" t="s">
+        <v>262</v>
+      </c>
+      <c r="J54" t="s">
         <v>263</v>
       </c>
-      <c r="J54" t="s">
+      <c r="K54" t="s">
         <v>264</v>
       </c>
-      <c r="K54" t="s">
+      <c r="L54" t="s">
         <v>265</v>
-      </c>
-      <c r="L54" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.35">
@@ -3464,13 +3467,13 @@
         <v>1</v>
       </c>
       <c r="B55" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D55" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G55" s="11">
         <v>9.9600000000000009</v>
@@ -3485,13 +3488,13 @@
         <v>1</v>
       </c>
       <c r="B56" t="s">
+        <v>342</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="D56" t="s">
         <v>343</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>340</v>
-      </c>
-      <c r="D56" t="s">
-        <v>344</v>
       </c>
       <c r="G56" s="11">
         <v>4</v>
@@ -3506,13 +3509,13 @@
         <v>1</v>
       </c>
       <c r="B57" t="s">
+        <v>266</v>
+      </c>
+      <c r="C57" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="C57" s="8" t="s">
+      <c r="D57" t="s">
         <v>268</v>
-      </c>
-      <c r="D57" t="s">
-        <v>269</v>
       </c>
       <c r="E57" t="s">
         <v>71</v>
@@ -3525,16 +3528,16 @@
         <v>9.86</v>
       </c>
       <c r="I57" t="s">
+        <v>269</v>
+      </c>
+      <c r="J57" t="s">
         <v>270</v>
       </c>
-      <c r="J57" t="s">
+      <c r="K57" t="s">
         <v>271</v>
       </c>
-      <c r="K57" t="s">
+      <c r="L57" t="s">
         <v>272</v>
-      </c>
-      <c r="L57" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="58" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
@@ -3542,13 +3545,13 @@
         <v>1</v>
       </c>
       <c r="B58" s="23" t="s">
+        <v>319</v>
+      </c>
+      <c r="C58" s="8" t="s">
         <v>320</v>
       </c>
-      <c r="C58" s="8" t="s">
-        <v>321</v>
-      </c>
       <c r="D58" s="22" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G58" s="11">
         <v>0.7</v>
@@ -3563,13 +3566,13 @@
         <v>4</v>
       </c>
       <c r="B59" t="s">
+        <v>277</v>
+      </c>
+      <c r="C59" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="C59" s="8" t="s">
+      <c r="F59" t="s">
         <v>279</v>
-      </c>
-      <c r="F59" t="s">
-        <v>280</v>
       </c>
       <c r="G59" s="11">
         <v>0.02</v>
@@ -3594,7 +3597,7 @@
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B62" s="21" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -3711,13 +3714,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D5" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G5" s="11">
         <v>0.17</v>
@@ -3732,13 +3735,13 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
+        <v>324</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="D6" t="s">
         <v>325</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="D6" t="s">
-        <v>326</v>
       </c>
       <c r="G6" s="11">
         <v>0.17</v>
@@ -3756,7 +3759,7 @@
         <v>41</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D7" t="s">
         <v>42</v>
@@ -3921,10 +3924,10 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F15" t="s">
         <v>87</v>
@@ -3987,7 +3990,7 @@
         <v>90</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D18" t="s">
         <v>92</v>
@@ -4026,16 +4029,16 @@
         <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>102</v>
       </c>
       <c r="D20" t="s">
+        <v>329</v>
+      </c>
+      <c r="E20" t="s">
         <v>330</v>
-      </c>
-      <c r="E20" t="s">
-        <v>331</v>
       </c>
       <c r="G20" s="11">
         <v>0.47</v>
@@ -4137,7 +4140,7 @@
         <v>128</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D25" t="s">
         <v>130</v>
@@ -4221,7 +4224,7 @@
         <v>149</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D29" t="s">
         <v>151</v>
@@ -4284,7 +4287,7 @@
         <v>164</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D32" t="s">
         <v>166</v>
@@ -4305,7 +4308,7 @@
         <v>169</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D33" t="s">
         <v>170</v>
@@ -4323,13 +4326,13 @@
         <v>1</v>
       </c>
       <c r="B34" t="s">
+        <v>345</v>
+      </c>
+      <c r="C34" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="C34" s="8" t="s">
-        <v>174</v>
-      </c>
       <c r="D34" t="s">
-        <v>175</v>
+        <v>346</v>
       </c>
       <c r="G34" s="11">
         <v>0.1</v>
@@ -4344,13 +4347,13 @@
         <v>1</v>
       </c>
       <c r="B35" t="s">
+        <v>177</v>
+      </c>
+      <c r="C35" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="C35" s="8" t="s">
-        <v>179</v>
-      </c>
       <c r="D35" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G35" s="11">
         <v>0.1</v>
@@ -4365,13 +4368,13 @@
         <v>1</v>
       </c>
       <c r="B36" t="s">
+        <v>182</v>
+      </c>
+      <c r="C36" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="D36" t="s">
         <v>184</v>
-      </c>
-      <c r="D36" t="s">
-        <v>185</v>
       </c>
       <c r="G36" s="11">
         <v>0.1</v>
@@ -4386,13 +4389,13 @@
         <v>1</v>
       </c>
       <c r="B37" t="s">
+        <v>187</v>
+      </c>
+      <c r="C37" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="D37" t="s">
         <v>189</v>
-      </c>
-      <c r="D37" t="s">
-        <v>190</v>
       </c>
       <c r="G37" s="11">
         <v>0.1</v>
@@ -4407,13 +4410,13 @@
         <v>18</v>
       </c>
       <c r="B38" t="s">
+        <v>192</v>
+      </c>
+      <c r="C38" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="F38" t="s">
         <v>194</v>
-      </c>
-      <c r="F38" t="s">
-        <v>195</v>
       </c>
       <c r="G38" s="11">
         <v>2.8000000000000001E-2</v>
@@ -4428,13 +4431,13 @@
         <v>1</v>
       </c>
       <c r="B39" t="s">
+        <v>195</v>
+      </c>
+      <c r="C39" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="D39" t="s">
         <v>197</v>
-      </c>
-      <c r="D39" t="s">
-        <v>198</v>
       </c>
       <c r="G39" s="11">
         <v>4.0199999999999996</v>
@@ -4449,13 +4452,13 @@
         <v>1</v>
       </c>
       <c r="B40" t="s">
+        <v>200</v>
+      </c>
+      <c r="C40" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="8" t="s">
+      <c r="D40" t="s">
         <v>202</v>
-      </c>
-      <c r="D40" t="s">
-        <v>203</v>
       </c>
       <c r="G40" s="11">
         <v>5.17</v>
@@ -4470,16 +4473,16 @@
         <v>2</v>
       </c>
       <c r="B41" t="s">
+        <v>203</v>
+      </c>
+      <c r="C41" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="C41" s="8" t="s">
+      <c r="D41" t="s">
         <v>205</v>
       </c>
-      <c r="D41" t="s">
+      <c r="E41" t="s">
         <v>206</v>
-      </c>
-      <c r="E41" t="s">
-        <v>207</v>
       </c>
       <c r="G41" s="11">
         <v>0.85</v>
@@ -4494,13 +4497,13 @@
         <v>1</v>
       </c>
       <c r="B42" t="s">
+        <v>207</v>
+      </c>
+      <c r="C42" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="D42" t="s">
         <v>209</v>
-      </c>
-      <c r="D42" t="s">
-        <v>210</v>
       </c>
       <c r="G42" s="11">
         <v>3.6</v>
@@ -4515,13 +4518,13 @@
         <v>2</v>
       </c>
       <c r="B43" t="s">
+        <v>285</v>
+      </c>
+      <c r="C43" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="C43" s="8" t="s">
-        <v>287</v>
-      </c>
       <c r="D43" s="13" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E43" t="s">
         <v>71</v>
@@ -4539,13 +4542,13 @@
         <v>2</v>
       </c>
       <c r="B44" t="s">
+        <v>222</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="D44" t="s">
         <v>223</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>341</v>
-      </c>
-      <c r="D44" t="s">
-        <v>224</v>
       </c>
       <c r="G44" s="11">
         <v>0.84</v>
@@ -4560,13 +4563,13 @@
         <v>1</v>
       </c>
       <c r="B45" t="s">
+        <v>227</v>
+      </c>
+      <c r="C45" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="C45" s="8" t="s">
+      <c r="D45" t="s">
         <v>229</v>
-      </c>
-      <c r="D45" t="s">
-        <v>230</v>
       </c>
       <c r="G45" s="11">
         <v>0.47</v>
@@ -4581,13 +4584,13 @@
         <v>2</v>
       </c>
       <c r="B46" t="s">
+        <v>230</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="D46" t="s">
         <v>231</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="D46" t="s">
-        <v>232</v>
       </c>
       <c r="G46" s="11">
         <v>1.03</v>
@@ -4602,13 +4605,13 @@
         <v>1</v>
       </c>
       <c r="B47" t="s">
+        <v>235</v>
+      </c>
+      <c r="C47" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="8" t="s">
+      <c r="D47" t="s">
         <v>237</v>
-      </c>
-      <c r="D47" t="s">
-        <v>238</v>
       </c>
       <c r="G47" s="11">
         <v>2.14</v>
@@ -4623,13 +4626,13 @@
         <v>1</v>
       </c>
       <c r="B48" t="s">
+        <v>241</v>
+      </c>
+      <c r="C48" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="C48" s="8" t="s">
+      <c r="D48" t="s">
         <v>243</v>
-      </c>
-      <c r="D48" t="s">
-        <v>244</v>
       </c>
       <c r="G48" s="11">
         <v>1.87</v>
@@ -4644,13 +4647,13 @@
         <v>1</v>
       </c>
       <c r="B49" t="s">
+        <v>245</v>
+      </c>
+      <c r="C49" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="C49" s="8" t="s">
+      <c r="D49" t="s">
         <v>247</v>
-      </c>
-      <c r="D49" t="s">
-        <v>248</v>
       </c>
       <c r="G49" s="11">
         <v>2.46</v>
@@ -4665,13 +4668,13 @@
         <v>1</v>
       </c>
       <c r="B50" t="s">
+        <v>249</v>
+      </c>
+      <c r="C50" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="C50" s="8" t="s">
+      <c r="D50" t="s">
         <v>251</v>
-      </c>
-      <c r="D50" t="s">
-        <v>252</v>
       </c>
       <c r="G50" s="11">
         <v>1.69</v>
@@ -4686,13 +4689,13 @@
         <v>1</v>
       </c>
       <c r="B51" t="s">
+        <v>254</v>
+      </c>
+      <c r="C51" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="C51" s="8" t="s">
+      <c r="D51" t="s">
         <v>256</v>
-      </c>
-      <c r="D51" t="s">
-        <v>257</v>
       </c>
       <c r="G51" s="11">
         <v>0.46</v>
@@ -4707,13 +4710,13 @@
         <v>1</v>
       </c>
       <c r="B52" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D52" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G52" s="11">
         <v>9.9600000000000009</v>
@@ -4728,13 +4731,13 @@
         <v>1</v>
       </c>
       <c r="B53" t="s">
+        <v>342</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="D53" t="s">
         <v>343</v>
-      </c>
-      <c r="C53" s="8" t="s">
-        <v>340</v>
-      </c>
-      <c r="D53" t="s">
-        <v>344</v>
       </c>
       <c r="G53" s="11">
         <v>4</v>
@@ -4749,16 +4752,16 @@
         <v>1</v>
       </c>
       <c r="B54" t="s">
+        <v>273</v>
+      </c>
+      <c r="C54" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="C54" s="8" t="s">
+      <c r="D54" t="s">
         <v>275</v>
       </c>
-      <c r="D54" t="s">
+      <c r="E54" t="s">
         <v>276</v>
-      </c>
-      <c r="E54" t="s">
-        <v>277</v>
       </c>
       <c r="G54" s="11">
         <v>0.45</v>
@@ -4773,13 +4776,13 @@
         <v>1</v>
       </c>
       <c r="B55" s="23" t="s">
+        <v>319</v>
+      </c>
+      <c r="C55" s="8" t="s">
         <v>320</v>
       </c>
-      <c r="C55" s="8" t="s">
-        <v>321</v>
-      </c>
       <c r="D55" s="22" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G55" s="11">
         <v>0.7</v>
@@ -4794,13 +4797,13 @@
         <v>4</v>
       </c>
       <c r="B56" t="s">
+        <v>277</v>
+      </c>
+      <c r="C56" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="C56" s="8" t="s">
+      <c r="F56" t="s">
         <v>279</v>
-      </c>
-      <c r="F56" t="s">
-        <v>280</v>
       </c>
       <c r="G56" s="11">
         <v>0.02</v>
@@ -4823,7 +4826,7 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B59" s="21" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -4884,7 +4887,7 @@
         <v>21</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D2" t="s">
         <v>23</v>
@@ -4926,7 +4929,7 @@
         <v>33</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D4" t="s">
         <v>35</v>
@@ -4944,13 +4947,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D5" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G5" s="11">
         <v>0.17</v>
@@ -4965,13 +4968,13 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
+        <v>324</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="D6" t="s">
         <v>325</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="D6" t="s">
-        <v>326</v>
       </c>
       <c r="G6" s="11">
         <v>0.17</v>
@@ -4989,7 +4992,7 @@
         <v>41</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D7" t="s">
         <v>42</v>
@@ -5028,10 +5031,10 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D9" t="s">
         <v>64</v>
@@ -5049,10 +5052,10 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D10" t="s">
         <v>70</v>
@@ -5157,7 +5160,7 @@
         <v>90</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D15" t="s">
         <v>92</v>
@@ -5178,7 +5181,7 @@
         <v>96</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D16" t="s">
         <v>98</v>
@@ -5196,13 +5199,13 @@
         <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>102</v>
       </c>
       <c r="D17" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G17" s="11">
         <v>0.47</v>
@@ -5262,7 +5265,7 @@
         <v>123</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D20" t="s">
         <v>125</v>
@@ -5283,7 +5286,7 @@
         <v>128</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D21" t="s">
         <v>130</v>
@@ -5364,13 +5367,13 @@
         <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F25" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G25" s="11">
         <v>2.8000000000000001E-2</v>
@@ -5385,13 +5388,13 @@
         <v>1</v>
       </c>
       <c r="B26" t="s">
+        <v>195</v>
+      </c>
+      <c r="C26" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="D26" t="s">
         <v>197</v>
-      </c>
-      <c r="D26" t="s">
-        <v>198</v>
       </c>
       <c r="G26" s="11">
         <v>4.0199999999999996</v>
@@ -5406,16 +5409,16 @@
         <v>1</v>
       </c>
       <c r="B27" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D27" t="s">
+        <v>205</v>
+      </c>
+      <c r="E27" t="s">
         <v>206</v>
-      </c>
-      <c r="E27" t="s">
-        <v>207</v>
       </c>
       <c r="G27" s="11">
         <v>0.85</v>
@@ -5430,13 +5433,13 @@
         <v>1</v>
       </c>
       <c r="B28" t="s">
+        <v>207</v>
+      </c>
+      <c r="C28" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="D28" t="s">
         <v>209</v>
-      </c>
-      <c r="D28" t="s">
-        <v>210</v>
       </c>
       <c r="G28" s="11">
         <v>3.6</v>
@@ -5451,13 +5454,13 @@
         <v>1</v>
       </c>
       <c r="B29" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D29" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E29" t="s">
         <v>71</v>
@@ -5490,13 +5493,13 @@
         <v>1</v>
       </c>
       <c r="B30" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E30" t="s">
         <v>71</v>
@@ -5514,13 +5517,13 @@
         <v>2</v>
       </c>
       <c r="B31" t="s">
+        <v>222</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="D31" t="s">
         <v>223</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>341</v>
-      </c>
-      <c r="D31" t="s">
-        <v>224</v>
       </c>
       <c r="G31" s="11">
         <v>0.84</v>
@@ -5535,13 +5538,13 @@
         <v>1</v>
       </c>
       <c r="B32" t="s">
+        <v>235</v>
+      </c>
+      <c r="C32" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="D32" t="s">
         <v>237</v>
-      </c>
-      <c r="D32" t="s">
-        <v>238</v>
       </c>
       <c r="G32" s="11">
         <v>2.14</v>
@@ -5556,13 +5559,13 @@
         <v>1</v>
       </c>
       <c r="B33" t="s">
+        <v>245</v>
+      </c>
+      <c r="C33" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="D33" t="s">
         <v>247</v>
-      </c>
-      <c r="D33" t="s">
-        <v>248</v>
       </c>
       <c r="G33" s="11">
         <v>2.46</v>
@@ -5577,13 +5580,13 @@
         <v>1</v>
       </c>
       <c r="B34" t="s">
+        <v>249</v>
+      </c>
+      <c r="C34" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="D34" t="s">
         <v>251</v>
-      </c>
-      <c r="D34" t="s">
-        <v>252</v>
       </c>
       <c r="G34" s="11">
         <v>1.69</v>
@@ -5598,13 +5601,13 @@
         <v>1</v>
       </c>
       <c r="B35" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D35" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G35" s="11">
         <v>9.9600000000000009</v>
@@ -5619,13 +5622,13 @@
         <v>1</v>
       </c>
       <c r="B36" t="s">
+        <v>342</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="D36" t="s">
         <v>343</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>340</v>
-      </c>
-      <c r="D36" t="s">
-        <v>344</v>
       </c>
       <c r="G36" s="11">
         <v>4</v>
@@ -5640,16 +5643,16 @@
         <v>1</v>
       </c>
       <c r="B37" t="s">
+        <v>273</v>
+      </c>
+      <c r="C37" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="D37" t="s">
         <v>275</v>
       </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
         <v>276</v>
-      </c>
-      <c r="E37" t="s">
-        <v>277</v>
       </c>
       <c r="G37" s="11">
         <v>0.45</v>
@@ -5664,13 +5667,13 @@
         <v>4</v>
       </c>
       <c r="B38" t="s">
+        <v>277</v>
+      </c>
+      <c r="C38" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="F38" t="s">
         <v>279</v>
-      </c>
-      <c r="F38" t="s">
-        <v>280</v>
       </c>
       <c r="G38" s="11">
         <v>0.02</v>
@@ -5746,7 +5749,7 @@
         <v>41</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D2" t="s">
         <v>42</v>
@@ -5769,7 +5772,7 @@
         <v>90</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D3" t="s">
         <v>92</v>
@@ -5789,16 +5792,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
+        <v>266</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="D4" t="s">
         <v>268</v>
       </c>
-      <c r="D4" t="s">
-        <v>269</v>
-      </c>
       <c r="E4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G4" s="5">
         <v>9.86</v>
@@ -5876,7 +5879,7 @@
         <v>41</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D2" t="s">
         <v>42</v>
@@ -5897,7 +5900,7 @@
         <v>149</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D3" t="s">
         <v>151</v>
@@ -5915,13 +5918,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
+        <v>260</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="D4" t="s">
         <v>262</v>
-      </c>
-      <c r="D4" t="s">
-        <v>263</v>
       </c>
       <c r="G4" s="5">
         <v>1.42</v>
@@ -5995,7 +5998,7 @@
         <v>41</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D2" t="s">
         <v>42</v>
@@ -6016,7 +6019,7 @@
         <v>128</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D3" t="s">
         <v>130</v>
@@ -6034,13 +6037,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E4" t="s">
         <v>71</v>
@@ -6118,7 +6121,7 @@
         <v>41</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D2" t="s">
         <v>42</v>
@@ -6139,7 +6142,7 @@
         <v>128</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D3" t="s">
         <v>130</v>
@@ -6157,13 +6160,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E4" t="s">
         <v>71</v>
